--- a/code/python/functions/bid_list/bid_lists/Excess List 9.8.26.xlsx
+++ b/code/python/functions/bid_list/bid_lists/Excess List 9.8.26.xlsx
@@ -1,46 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nucor-my.sharepoint.com/personal/alex_holifield_nucor_com/Documents/Documents/Secondary Market/2026 Week 36/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{82940127-86F6-401E-A272-E8A2927912B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38C00F0B-712D-4EB4-A220-20FD1B6AFB6F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Excess List" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" name="Excess List" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Excess List'!$A$1:$AU$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Excess List'!$A$1:$AU$32</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Bids</t>
   </si>
@@ -830,24 +828,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000;\-0.0000"/>
+    <numFmt numFmtId="267" formatCode="0.0000;\-0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="9"/>
-      <color rgb="FF333333"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF333333"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -860,14 +864,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF319663"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF319663"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -895,44 +897,59 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="267" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -978,7 +995,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1030,7 +1047,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1091,346 +1108,349 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EAB5A604-B7A6-46BC-B492-2D323CFAF21A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AT33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="15" width="20.140625" style="6" customWidth="1"/>
-    <col min="16" max="16" width="57.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8" style="6" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="4.7109375" style="6" customWidth="1"/>
-    <col min="48" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="15" style="6" width="20.140625" customWidth="1"/>
+    <col min="16" max="16" style="6" width="57.57421875" customWidth="1"/>
+    <col min="17" max="17" style="6" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" style="6" width="11.57421875" customWidth="1"/>
+    <col min="19" max="19" style="6" width="11.00390625" customWidth="1"/>
+    <col min="20" max="20" style="6" width="12.57421875" customWidth="1"/>
+    <col min="21" max="21" style="6" width="11.140625" customWidth="1"/>
+    <col min="22" max="22" style="6" width="9.8515625" customWidth="1"/>
+    <col min="23" max="23" style="6" width="11.57421875" customWidth="1"/>
+    <col min="24" max="24" style="6" width="8.28125" customWidth="1"/>
+    <col min="25" max="25" style="6" width="11.140625" customWidth="1"/>
+    <col min="26" max="26" style="6" width="8.57421875" customWidth="1"/>
+    <col min="27" max="27" style="6" width="12.00390625" customWidth="1"/>
+    <col min="28" max="28" style="6" width="12.28125" customWidth="1"/>
+    <col min="29" max="29" style="6" width="7.421875" customWidth="1"/>
+    <col min="30" max="30" style="6" width="8.00390625" customWidth="1"/>
+    <col min="31" max="31" style="6" width="8.57421875" customWidth="1"/>
+    <col min="32" max="32" style="6" width="7.7109375" customWidth="1"/>
+    <col min="33" max="33" style="6" width="10.8515625" customWidth="1"/>
+    <col min="34" max="34" style="6" width="12.8515625" customWidth="1"/>
+    <col min="35" max="35" style="6" width="5.28125" customWidth="1"/>
+    <col min="36" max="37" style="6" width="10.57421875" customWidth="1"/>
+    <col min="38" max="38" style="6" width="9.28125" customWidth="1"/>
+    <col min="39" max="39" style="6" width="6.8515625" customWidth="1"/>
+    <col min="40" max="40" style="6" width="9.57421875" customWidth="1"/>
+    <col min="41" max="41" style="6" width="9.140625" customWidth="1"/>
+    <col min="42" max="42" style="6" width="7.57421875" customWidth="1"/>
+    <col min="43" max="43" style="6" width="9.421875" customWidth="1"/>
+    <col min="44" max="44" style="6" width="12.57421875" customWidth="1"/>
+    <col min="45" max="45" style="6" width="10.57421875" customWidth="1"/>
+    <col min="46" max="46" style="6" width="10.00390625" customWidth="1"/>
+    <col min="47" max="47" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="2" customFormat="1" ht="33">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="33" customHeight="1" s="1" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="2" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>46</v>
@@ -1457,10 +1477,10 @@
         <v>40490</v>
       </c>
       <c r="J2" s="5">
-        <v>20.245000000000001</v>
+        <v>20.245</v>
       </c>
       <c r="K2" s="5">
-        <v>2.7699999999999999E-2</v>
+        <v>0.0277</v>
       </c>
       <c r="L2" s="5">
         <v>51.625</v>
@@ -1491,58 +1511,58 @@
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="AA2" s="5">
         <v>1.63</v>
       </c>
       <c r="AB2" s="5">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC2" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AD2" s="5">
-        <v>0.51900000000000002</v>
+        <v>0.519</v>
       </c>
       <c r="AE2" s="5">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="AF2" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG2" s="5">
-        <v>0.33100000000000002</v>
+        <v>0.331</v>
       </c>
       <c r="AH2" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI2" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AJ2" s="5">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AK2" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AL2" s="5">
-        <v>3.2000000000000002E-3</v>
+        <v>0.0032</v>
       </c>
       <c r="AM2" s="5">
         <v>0</v>
       </c>
       <c r="AN2" s="5">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="AO2" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP2" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ2" s="5">
-        <v>8.6E-3</v>
+        <v>0.0086</v>
       </c>
       <c r="AR2" s="3" t="s">
         <v>56</v>
@@ -1554,7 +1574,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:46" s="2" customFormat="1" ht="110.25">
+    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>46</v>
@@ -1581,10 +1601,10 @@
         <v>41330</v>
       </c>
       <c r="J3" s="5">
-        <v>20.664999999999999</v>
+        <v>20.665</v>
       </c>
       <c r="K3" s="5">
-        <v>2.2599999999999999E-2</v>
+        <v>0.0226</v>
       </c>
       <c r="L3" s="5">
         <v>58.625</v>
@@ -1615,58 +1635,58 @@
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="AA3" s="5">
-        <v>0.33100000000000002</v>
+        <v>0.331</v>
       </c>
       <c r="AB3" s="5">
         <v>0.01</v>
       </c>
       <c r="AC3" s="5">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AD3" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AE3" s="5">
         <v>0.106</v>
       </c>
       <c r="AF3" s="5">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AG3" s="5">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH3" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI3" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ3" s="5">
         <v>0.03</v>
       </c>
       <c r="AK3" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL3" s="5">
-        <v>5.0000000000000001E-4</v>
+        <v>0.0005</v>
       </c>
       <c r="AM3" s="5">
         <v>0</v>
       </c>
       <c r="AN3" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO3" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AP3" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ3" s="5">
-        <v>7.3000000000000001E-3</v>
+        <v>0.0073</v>
       </c>
       <c r="AR3" s="3" t="s">
         <v>56</v>
@@ -1678,7 +1698,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="4" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>46</v>
@@ -1708,7 +1728,7 @@
         <v>16.48</v>
       </c>
       <c r="K4" s="5">
-        <v>2.76E-2</v>
+        <v>0.0276</v>
       </c>
       <c r="L4" s="5">
         <v>36.3125</v>
@@ -1753,58 +1773,58 @@
         <v>22</v>
       </c>
       <c r="Z4" s="5">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AA4" s="5">
         <v>1.613</v>
       </c>
       <c r="AB4" s="5">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC4" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD4" s="5">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="AE4" s="5">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="AF4" s="5">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG4" s="5">
-        <v>0.31900000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="AH4" s="5">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AI4" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ4" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AK4" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AL4" s="5">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AM4" s="5">
         <v>0</v>
       </c>
       <c r="AN4" s="5">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="AO4" s="5">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP4" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ4" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>0.0071</v>
       </c>
       <c r="AR4" s="3" t="s">
         <v>56</v>
@@ -1816,7 +1836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:46" s="2" customFormat="1" ht="143.25">
+    <row r="5" ht="143.25" customHeight="1" s="1" customFormat="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>46</v>
@@ -1843,10 +1863,10 @@
         <v>32370</v>
       </c>
       <c r="J5" s="5">
-        <v>16.184999999999999</v>
+        <v>16.185</v>
       </c>
       <c r="K5" s="5">
-        <v>6.93E-2</v>
+        <v>0.0693</v>
       </c>
       <c r="L5" s="5">
         <v>63.3125</v>
@@ -1891,58 +1911,58 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AA5" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AB5" s="5">
         <v>0.01</v>
       </c>
       <c r="AC5" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD5" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AE5" s="5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF5" s="5">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AG5" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH5" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AI5" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ5" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AK5" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AL5" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AM5" s="5">
         <v>0</v>
       </c>
       <c r="AN5" s="5">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="AO5" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP5" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ5" s="5">
-        <v>5.5999999999999999E-3</v>
+        <v>0.0056</v>
       </c>
       <c r="AR5" s="3" t="s">
         <v>56</v>
@@ -1954,7 +1974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:46" s="2" customFormat="1" ht="143.25">
+    <row r="6" ht="143.25" customHeight="1" s="1" customFormat="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>46</v>
@@ -1981,10 +2001,10 @@
         <v>33870</v>
       </c>
       <c r="J6" s="5">
-        <v>16.934999999999999</v>
+        <v>16.935</v>
       </c>
       <c r="K6" s="5">
-        <v>6.9099999999999995E-2</v>
+        <v>0.0691</v>
       </c>
       <c r="L6" s="5">
         <v>63.375</v>
@@ -2029,58 +2049,58 @@
         <v>0</v>
       </c>
       <c r="Z6" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AA6" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AB6" s="5">
         <v>0.01</v>
       </c>
       <c r="AC6" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD6" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AE6" s="5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF6" s="5">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AG6" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH6" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AI6" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ6" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AK6" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AL6" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AM6" s="5">
         <v>0</v>
       </c>
       <c r="AN6" s="5">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="AO6" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP6" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ6" s="5">
-        <v>5.5999999999999999E-3</v>
+        <v>0.0056</v>
       </c>
       <c r="AR6" s="3" t="s">
         <v>56</v>
@@ -2092,7 +2112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="2" customFormat="1" ht="143.25">
+    <row r="7" ht="143.25" customHeight="1" s="1" customFormat="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>46</v>
@@ -2122,7 +2142,7 @@
         <v>20.25</v>
       </c>
       <c r="K7" s="5">
-        <v>3.15E-2</v>
+        <v>0.0315</v>
       </c>
       <c r="L7" s="5">
         <v>53.0625</v>
@@ -2167,58 +2187,58 @@
         <v>22</v>
       </c>
       <c r="Z7" s="5">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="AA7" s="5">
-        <v>1.6020000000000001</v>
+        <v>1.602</v>
       </c>
       <c r="AB7" s="5">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="AC7" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AD7" s="5">
-        <v>0.51200000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="AE7" s="5">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="AF7" s="5">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG7" s="5">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="AH7" s="5">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI7" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ7" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AK7" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AL7" s="5">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AM7" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN7" s="5">
         <v>0.08</v>
       </c>
       <c r="AO7" s="5">
-        <v>1.4E-3</v>
+        <v>0.0014</v>
       </c>
       <c r="AP7" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ7" s="5">
-        <v>7.4999999999999997E-3</v>
+        <v>0.0075</v>
       </c>
       <c r="AR7" s="3" t="s">
         <v>56</v>
@@ -2230,7 +2250,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="8" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>46</v>
@@ -2260,7 +2280,7 @@
         <v>22.62</v>
       </c>
       <c r="K8" s="5">
-        <v>5.6899999999999999E-2</v>
+        <v>0.0569</v>
       </c>
       <c r="L8" s="5">
         <v>60.0625</v>
@@ -2291,58 +2311,58 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AA8" s="5">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="AB8" s="5">
         <v>0.01</v>
       </c>
       <c r="AC8" s="5">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD8" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AE8" s="5">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="AF8" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG8" s="5">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AH8" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI8" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ8" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AK8" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL8" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AM8" s="5">
         <v>0</v>
       </c>
       <c r="AN8" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AO8" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP8" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ8" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.0064</v>
       </c>
       <c r="AR8" s="3" t="s">
         <v>56</v>
@@ -2354,7 +2374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="9" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -2381,10 +2401,10 @@
         <v>34690</v>
       </c>
       <c r="J9" s="5">
-        <v>17.344999999999999</v>
+        <v>17.345</v>
       </c>
       <c r="K9" s="5">
-        <v>2.7799999999999998E-2</v>
+        <v>0.0278</v>
       </c>
       <c r="L9" s="5">
         <v>37.1875</v>
@@ -2429,58 +2449,58 @@
         <v>30</v>
       </c>
       <c r="Z9" s="5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="AA9" s="5">
-        <v>1.4470000000000001</v>
+        <v>1.447</v>
       </c>
       <c r="AB9" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AC9" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AD9" s="5">
         <v>0.309</v>
       </c>
       <c r="AE9" s="5">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="AF9" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG9" s="5">
-        <v>0.33200000000000002</v>
+        <v>0.332</v>
       </c>
       <c r="AH9" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI9" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ9" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AK9" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AL9" s="5">
-        <v>3.5999999999999999E-3</v>
+        <v>0.0036</v>
       </c>
       <c r="AM9" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN9" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO9" s="5">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP9" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ9" s="5">
-        <v>7.4999999999999997E-3</v>
+        <v>0.0075</v>
       </c>
       <c r="AR9" s="3" t="s">
         <v>56</v>
@@ -2492,7 +2512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="10" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>46</v>
@@ -2519,10 +2539,10 @@
         <v>32970</v>
       </c>
       <c r="J10" s="5">
-        <v>16.484999999999999</v>
+        <v>16.485</v>
       </c>
       <c r="K10" s="5">
-        <v>4.7399999999999998E-2</v>
+        <v>0.0474</v>
       </c>
       <c r="L10" s="5">
         <v>36.125</v>
@@ -2553,58 +2573,58 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA10" s="5">
-        <v>1.4470000000000001</v>
+        <v>1.447</v>
       </c>
       <c r="AB10" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AC10" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AD10" s="5">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="AE10" s="5">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AF10" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG10" s="5">
-        <v>0.33200000000000002</v>
+        <v>0.332</v>
       </c>
       <c r="AH10" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI10" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AJ10" s="5">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="AK10" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AL10" s="5">
-        <v>3.3999999999999998E-3</v>
+        <v>0.0034</v>
       </c>
       <c r="AM10" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN10" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO10" s="5">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP10" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ10" s="5">
-        <v>6.7999999999999996E-3</v>
+        <v>0.0068</v>
       </c>
       <c r="AR10" s="3" t="s">
         <v>56</v>
@@ -2616,7 +2636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:46" s="2" customFormat="1" ht="209.25">
+    <row r="11" ht="209.25" customHeight="1" s="1" customFormat="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>46</v>
@@ -2643,10 +2663,10 @@
         <v>39660</v>
       </c>
       <c r="J11" s="5">
-        <v>19.829999999999998</v>
+        <v>19.83</v>
       </c>
       <c r="K11" s="5">
-        <v>5.5500000000000001E-2</v>
+        <v>0.0555</v>
       </c>
       <c r="L11" s="5">
         <v>44.3125</v>
@@ -2673,58 +2693,58 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
-        <v>4.1000000000000003E-3</v>
+        <v>0.0041</v>
       </c>
       <c r="AA11" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AB11" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AC11" s="5">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AD11" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AE11" s="5">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="AF11" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="AG11" s="5">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AH11" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI11" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ11" s="5">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK11" s="5">
         <v>0</v>
       </c>
       <c r="AL11" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AM11" s="5">
         <v>0</v>
       </c>
       <c r="AN11" s="5">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="AO11" s="5">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP11" s="5">
         <v>0</v>
       </c>
       <c r="AQ11" s="5">
-        <v>6.1000000000000004E-3</v>
+        <v>0.0061</v>
       </c>
       <c r="AR11" s="3" t="s">
         <v>56</v>
@@ -2736,7 +2756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="12" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>46</v>
@@ -2748,7 +2768,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="4">
-        <v>2185183.2000000002</v>
+        <v>2185183.2</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>58</v>
@@ -2763,7 +2783,7 @@
         <v>18570</v>
       </c>
       <c r="J12" s="5">
-        <v>9.2850000000000001</v>
+        <v>9.285</v>
       </c>
       <c r="K12" s="5">
         <v>0.1193</v>
@@ -2797,58 +2817,58 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
-        <v>5.8000000000000003E-2</v>
+        <v>0.058</v>
       </c>
       <c r="AA12" s="5">
-        <v>0.36299999999999999</v>
+        <v>0.363</v>
       </c>
       <c r="AB12" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC12" s="5">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AD12" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AE12" s="5">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AF12" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG12" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH12" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI12" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ12" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AK12" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL12" s="5">
-        <v>4.1000000000000003E-3</v>
+        <v>0.0041</v>
       </c>
       <c r="AM12" s="5">
         <v>0</v>
       </c>
       <c r="AN12" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO12" s="5">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AP12" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ12" s="5">
-        <v>6.8999999999999999E-3</v>
+        <v>0.0069</v>
       </c>
       <c r="AR12" s="3" t="s">
         <v>56</v>
@@ -2860,7 +2880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:46" s="2" customFormat="1" ht="320.25">
+    <row r="13" ht="320.25" customHeight="1" s="1" customFormat="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>46</v>
@@ -2890,7 +2910,7 @@
         <v>10.95</v>
       </c>
       <c r="K13" s="5">
-        <v>5.3600000000000002E-2</v>
+        <v>0.0536</v>
       </c>
       <c r="L13" s="5">
         <v>59.125</v>
@@ -2924,55 +2944,55 @@
         <v>0.185</v>
       </c>
       <c r="AA13" s="5">
-        <v>0.66300000000000003</v>
+        <v>0.663</v>
       </c>
       <c r="AB13" s="5">
         <v>0.01</v>
       </c>
       <c r="AC13" s="5">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AD13" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AE13" s="5">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="AF13" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG13" s="5">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH13" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI13" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ13" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK13" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL13" s="5">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AM13" s="5">
         <v>0</v>
       </c>
       <c r="AN13" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO13" s="5">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP13" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ13" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>0.0071</v>
       </c>
       <c r="AR13" s="3" t="s">
         <v>56</v>
@@ -2984,7 +3004,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="14" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>46</v>
@@ -3014,7 +3034,7 @@
         <v>24.18</v>
       </c>
       <c r="K14" s="5">
-        <v>2.3900000000000001E-2</v>
+        <v>0.0239</v>
       </c>
       <c r="L14" s="5">
         <v>55.5625</v>
@@ -3057,34 +3077,34 @@
         <v>41</v>
       </c>
       <c r="Z14" s="5">
-        <v>3.7000000000000002E-3</v>
+        <v>0.0037</v>
       </c>
       <c r="AA14" s="5">
         <v>0.04</v>
       </c>
       <c r="AB14" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AC14" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD14" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>0.021</v>
       </c>
       <c r="AE14" s="5">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="AF14" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AG14" s="5">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AH14" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI14" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ14" s="5">
         <v>0.06</v>
@@ -3093,22 +3113,22 @@
         <v>0</v>
       </c>
       <c r="AL14" s="5">
-        <v>3.0999999999999999E-3</v>
+        <v>0.0031</v>
       </c>
       <c r="AM14" s="5">
         <v>0</v>
       </c>
       <c r="AN14" s="5">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="AO14" s="5">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AP14" s="5">
         <v>0</v>
       </c>
       <c r="AQ14" s="5">
-        <v>3.8E-3</v>
+        <v>0.0038</v>
       </c>
       <c r="AR14" s="3" t="s">
         <v>56</v>
@@ -3120,7 +3140,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:46" s="2" customFormat="1" ht="87.75">
+    <row r="15" ht="87.75" customHeight="1" s="1" customFormat="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -3147,10 +3167,10 @@
         <v>34160</v>
       </c>
       <c r="J15" s="5">
-        <v>17.079999999999998</v>
+        <v>17.08</v>
       </c>
       <c r="K15" s="5">
-        <v>4.1500000000000002E-2</v>
+        <v>0.0415</v>
       </c>
       <c r="L15" s="5">
         <v>60.125</v>
@@ -3195,58 +3215,58 @@
         <v>0</v>
       </c>
       <c r="Z15" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AA15" s="5">
-        <v>0.61099999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="AB15" s="5">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC15" s="5">
-        <v>5.9999999999999995E-4</v>
+        <v>0.0006</v>
       </c>
       <c r="AD15" s="5">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="AE15" s="5">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="AF15" s="5">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG15" s="5">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AH15" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI15" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AJ15" s="5">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AK15" s="5">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="AL15" s="5">
-        <v>3.3E-3</v>
+        <v>0.0033</v>
       </c>
       <c r="AM15" s="5">
         <v>0</v>
       </c>
       <c r="AN15" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO15" s="5">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP15" s="5">
         <v>0</v>
       </c>
       <c r="AQ15" s="5">
-        <v>1.26E-2</v>
+        <v>0.0126</v>
       </c>
       <c r="AR15" s="3" t="s">
         <v>56</v>
@@ -3258,7 +3278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="16" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>46</v>
@@ -3288,7 +3308,7 @@
         <v>11.45</v>
       </c>
       <c r="K16" s="5">
-        <v>2.7799999999999998E-2</v>
+        <v>0.0278</v>
       </c>
       <c r="L16" s="5">
         <v>58.3125</v>
@@ -3333,58 +3353,58 @@
         <v>0</v>
       </c>
       <c r="Z16" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AA16" s="5">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="AB16" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC16" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD16" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE16" s="5">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="AF16" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG16" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH16" s="5">
         <v>0.01</v>
       </c>
       <c r="AI16" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ16" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AK16" s="5">
         <v>0</v>
       </c>
       <c r="AL16" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AM16" s="5">
         <v>0</v>
       </c>
       <c r="AN16" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO16" s="5">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP16" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ16" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AR16" s="3" t="s">
         <v>56</v>
@@ -3396,7 +3416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:46" s="2" customFormat="1" ht="132.75">
+    <row r="17" ht="132.75" customHeight="1" s="1" customFormat="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>46</v>
@@ -3408,7 +3428,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="4">
-        <v>2188829.2000000002</v>
+        <v>2188829.2</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>74</v>
@@ -3423,10 +3443,10 @@
         <v>20830</v>
       </c>
       <c r="J17" s="5">
-        <v>10.414999999999999</v>
+        <v>10.415</v>
       </c>
       <c r="K17" s="5">
-        <v>2.7799999999999998E-2</v>
+        <v>0.0278</v>
       </c>
       <c r="L17" s="5">
         <v>58.3125</v>
@@ -3471,58 +3491,58 @@
         <v>0</v>
       </c>
       <c r="Z17" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AA17" s="5">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="AB17" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC17" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD17" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE17" s="5">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="AF17" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG17" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH17" s="5">
         <v>0.01</v>
       </c>
       <c r="AI17" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ17" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AK17" s="5">
         <v>0</v>
       </c>
       <c r="AL17" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AM17" s="5">
         <v>0</v>
       </c>
       <c r="AN17" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO17" s="5">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP17" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ17" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AR17" s="3" t="s">
         <v>56</v>
@@ -3534,7 +3554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:46" s="2" customFormat="1" ht="198.75">
+    <row r="18" ht="198.75" customHeight="1" s="1" customFormat="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>46</v>
@@ -3561,10 +3581,10 @@
         <v>38630</v>
       </c>
       <c r="J18" s="5">
-        <v>19.315000000000001</v>
+        <v>19.315</v>
       </c>
       <c r="K18" s="5">
-        <v>2.53E-2</v>
+        <v>0.0253</v>
       </c>
       <c r="L18" s="5">
         <v>59.0625</v>
@@ -3594,7 +3614,7 @@
         <v>49.2</v>
       </c>
       <c r="U18" s="5">
-        <v>39.799999999999997</v>
+        <v>39.8</v>
       </c>
       <c r="V18" s="5">
         <v>0</v>
@@ -3609,58 +3629,58 @@
         <v>0</v>
       </c>
       <c r="Z18" s="5">
-        <v>4.3E-3</v>
+        <v>0.0043</v>
       </c>
       <c r="AA18" s="5">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AB18" s="5">
         <v>0.01</v>
       </c>
       <c r="AC18" s="5">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD18" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AE18" s="5">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="AF18" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG18" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AH18" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ18" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK18" s="5">
         <v>0</v>
       </c>
       <c r="AL18" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AM18" s="5">
         <v>0</v>
       </c>
       <c r="AN18" s="5">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="AO18" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AP18" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ18" s="5">
-        <v>5.4999999999999997E-3</v>
+        <v>0.0055</v>
       </c>
       <c r="AR18" s="3" t="s">
         <v>56</v>
@@ -3672,7 +3692,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="19" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>46</v>
@@ -3699,10 +3719,10 @@
         <v>23030</v>
       </c>
       <c r="J19" s="5">
-        <v>11.515000000000001</v>
+        <v>11.515</v>
       </c>
       <c r="K19" s="5">
-        <v>2.5700000000000001E-2</v>
+        <v>0.0257</v>
       </c>
       <c r="L19" s="5">
         <v>52.125</v>
@@ -3747,34 +3767,34 @@
         <v>0</v>
       </c>
       <c r="Z19" s="5">
-        <v>3.5999999999999999E-3</v>
+        <v>0.0036</v>
       </c>
       <c r="AA19" s="5">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AB19" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC19" s="5">
-        <v>1.6999999999999999E-3</v>
+        <v>0.0017</v>
       </c>
       <c r="AD19" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>0.021</v>
       </c>
       <c r="AE19" s="5">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="AF19" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AG19" s="5">
         <v>0.04</v>
       </c>
       <c r="AH19" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI19" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ19" s="5">
         <v>0.04</v>
@@ -3783,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="AL19" s="5">
-        <v>5.3E-3</v>
+        <v>0.0053</v>
       </c>
       <c r="AM19" s="5">
         <v>0</v>
       </c>
       <c r="AN19" s="5">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AO19" s="5">
-        <v>1.6999999999999999E-3</v>
+        <v>0.0017</v>
       </c>
       <c r="AP19" s="5">
         <v>0</v>
       </c>
       <c r="AQ19" s="5">
-        <v>5.7000000000000002E-3</v>
+        <v>0.0057</v>
       </c>
       <c r="AR19" s="3" t="s">
         <v>56</v>
@@ -3810,7 +3830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="20" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -3840,7 +3860,7 @@
         <v>11.53</v>
       </c>
       <c r="K20" s="5">
-        <v>2.58E-2</v>
+        <v>0.0258</v>
       </c>
       <c r="L20" s="5">
         <v>52.125</v>
@@ -3885,58 +3905,58 @@
         <v>0</v>
       </c>
       <c r="Z20" s="5">
-        <v>3.8E-3</v>
+        <v>0.0038</v>
       </c>
       <c r="AA20" s="5">
         <v>0.04</v>
       </c>
       <c r="AB20" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC20" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AD20" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AE20" s="5">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="AF20" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG20" s="5">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AH20" s="5">
         <v>0.01</v>
       </c>
       <c r="AI20" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ20" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AK20" s="5">
         <v>0</v>
       </c>
       <c r="AL20" s="5">
-        <v>4.5999999999999999E-3</v>
+        <v>0.0046</v>
       </c>
       <c r="AM20" s="5">
         <v>0</v>
       </c>
       <c r="AN20" s="5">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="AO20" s="5">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP20" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ20" s="5">
-        <v>4.4999999999999997E-3</v>
+        <v>0.0045</v>
       </c>
       <c r="AR20" s="3" t="s">
         <v>56</v>
@@ -3948,7 +3968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="21" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>46</v>
@@ -3960,7 +3980,7 @@
         <v>47</v>
       </c>
       <c r="E21" s="4">
-        <v>2192906.2000000002</v>
+        <v>2192906.2</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>66</v>
@@ -3975,10 +3995,10 @@
         <v>21310</v>
       </c>
       <c r="J21" s="5">
-        <v>10.654999999999999</v>
+        <v>10.655</v>
       </c>
       <c r="K21" s="5">
-        <v>2.5700000000000001E-2</v>
+        <v>0.0257</v>
       </c>
       <c r="L21" s="5">
         <v>52.125</v>
@@ -4023,58 +4043,58 @@
         <v>0</v>
       </c>
       <c r="Z21" s="5">
-        <v>3.8E-3</v>
+        <v>0.0038</v>
       </c>
       <c r="AA21" s="5">
         <v>0.04</v>
       </c>
       <c r="AB21" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC21" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AD21" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AE21" s="5">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="AF21" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG21" s="5">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AH21" s="5">
         <v>0.01</v>
       </c>
       <c r="AI21" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ21" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AK21" s="5">
         <v>0</v>
       </c>
       <c r="AL21" s="5">
-        <v>4.5999999999999999E-3</v>
+        <v>0.0046</v>
       </c>
       <c r="AM21" s="5">
         <v>0</v>
       </c>
       <c r="AN21" s="5">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="AO21" s="5">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP21" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ21" s="5">
-        <v>4.4999999999999997E-3</v>
+        <v>0.0045</v>
       </c>
       <c r="AR21" s="3" t="s">
         <v>56</v>
@@ -4086,7 +4106,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:46" s="2" customFormat="1" ht="87.75">
+    <row r="22" ht="87.75" customHeight="1" s="1" customFormat="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>46</v>
@@ -4116,7 +4136,7 @@
         <v>19.6265</v>
       </c>
       <c r="K22" s="5">
-        <v>3.15E-2</v>
+        <v>0.0315</v>
       </c>
       <c r="L22" s="5">
         <v>53</v>
@@ -4161,58 +4181,58 @@
         <v>23</v>
       </c>
       <c r="Z22" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AA22" s="5">
-        <v>1.5409999999999999</v>
+        <v>1.541</v>
       </c>
       <c r="AB22" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AC22" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AD22" s="5">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="AE22" s="5">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="AF22" s="5">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AG22" s="5">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="AH22" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AI22" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ22" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AK22" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AL22" s="5">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AM22" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN22" s="5">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="AO22" s="5">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP22" s="5">
-        <v>4.0000000000000002E-4</v>
+        <v>0.0004</v>
       </c>
       <c r="AQ22" s="5">
-        <v>7.3000000000000001E-3</v>
+        <v>0.0073</v>
       </c>
       <c r="AR22" s="3" t="s">
         <v>56</v>
@@ -4224,7 +4244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:46" s="2" customFormat="1" ht="143.25">
+    <row r="23" ht="143.25" customHeight="1" s="1" customFormat="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>107</v>
@@ -4251,10 +4271,10 @@
         <v>45568</v>
       </c>
       <c r="J23" s="5">
-        <v>22.783999999999999</v>
+        <v>22.784</v>
       </c>
       <c r="K23" s="5">
-        <v>7.0699999999999999E-2</v>
+        <v>0.0707</v>
       </c>
       <c r="L23" s="5">
         <v>62.625</v>
@@ -4281,58 +4301,58 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="AA23" s="5">
-        <v>0.49099999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="AB23" s="5">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC23" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD23" s="5">
-        <v>1.9E-2</v>
+        <v>0.019</v>
       </c>
       <c r="AE23" s="5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF23" s="5">
         <v>0.04</v>
       </c>
       <c r="AG23" s="5">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH23" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI23" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ23" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AK23" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL23" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AM23" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN23" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO23" s="5">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP23" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ23" s="5">
-        <v>7.6E-3</v>
+        <v>0.0076</v>
       </c>
       <c r="AR23" s="3" t="s">
         <v>56</v>
@@ -4344,7 +4364,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:46" s="2" customFormat="1" ht="243">
+    <row r="24" ht="243" customHeight="1" s="1" customFormat="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>107</v>
@@ -4371,10 +4391,10 @@
         <v>39194</v>
       </c>
       <c r="J24" s="5">
-        <v>19.597000000000001</v>
+        <v>19.597</v>
       </c>
       <c r="K24" s="5">
-        <v>3.2199999999999999E-2</v>
+        <v>0.0322</v>
       </c>
       <c r="L24" s="5">
         <v>56.5</v>
@@ -4401,58 +4421,58 @@
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AA24" s="5">
-        <v>1.5980000000000001</v>
+        <v>1.598</v>
       </c>
       <c r="AB24" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC24" s="5">
-        <v>6.9999999999999999E-4</v>
+        <v>0.0007</v>
       </c>
       <c r="AD24" s="5">
         <v>0.505</v>
       </c>
       <c r="AE24" s="5">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="AF24" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG24" s="5">
         <v>0.315</v>
       </c>
       <c r="AH24" s="5">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI24" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ24" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AK24" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AL24" s="5">
-        <v>5.7999999999999996E-3</v>
+        <v>0.0058</v>
       </c>
       <c r="AM24" s="5">
         <v>0</v>
       </c>
       <c r="AN24" s="5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AO24" s="5">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP24" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ24" s="5">
-        <v>7.3000000000000001E-3</v>
+        <v>0.0073</v>
       </c>
       <c r="AR24" s="3" t="s">
         <v>56</v>
@@ -4464,7 +4484,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:46" s="2" customFormat="1" ht="99">
+    <row r="25" ht="99" customHeight="1" s="1" customFormat="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>107</v>
@@ -4476,7 +4496,7 @@
         <v>108</v>
       </c>
       <c r="E25" s="4">
-        <v>2195420.2000000002</v>
+        <v>2195420.2</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>66</v>
@@ -4491,10 +4511,10 @@
         <v>23810</v>
       </c>
       <c r="J25" s="5">
-        <v>11.904999999999999</v>
+        <v>11.905</v>
       </c>
       <c r="K25" s="5">
-        <v>4.7199999999999999E-2</v>
+        <v>0.0472</v>
       </c>
       <c r="L25" s="5">
         <v>39.1875</v>
@@ -4521,58 +4541,58 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
-        <v>4.7999999999999996E-3</v>
+        <v>0.0048</v>
       </c>
       <c r="AA25" s="5">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AB25" s="5">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC25" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD25" s="5">
-        <v>2.1000000000000001E-2</v>
+        <v>0.021</v>
       </c>
       <c r="AE25" s="5">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="AF25" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG25" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AH25" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI25" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ25" s="5">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AK25" s="5">
         <v>0</v>
       </c>
       <c r="AL25" s="5">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AM25" s="5">
         <v>0</v>
       </c>
       <c r="AN25" s="5">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="AO25" s="5">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP25" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ25" s="5">
-        <v>6.1000000000000004E-3</v>
+        <v>0.0061</v>
       </c>
       <c r="AR25" s="3" t="s">
         <v>56</v>
@@ -4584,7 +4604,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:46" s="2" customFormat="1" ht="99">
+    <row r="26" ht="99" customHeight="1" s="1" customFormat="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>117</v>
@@ -4614,10 +4634,10 @@
         <v>5.13</v>
       </c>
       <c r="K26" s="5">
-        <v>2.7699999999999999E-2</v>
+        <v>0.0277</v>
       </c>
       <c r="L26" s="5">
-        <v>46.082599999999999</v>
+        <v>46.0826</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>120</v>
@@ -4659,58 +4679,58 @@
         <v>0</v>
       </c>
       <c r="Z26" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AA26" s="5">
         <v>0.128</v>
       </c>
       <c r="AB26" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AC26" s="5">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AD26" s="5">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="AE26" s="5">
         <v>0.113</v>
       </c>
       <c r="AF26" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AG26" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AH26" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI26" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ26" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AK26" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL26" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AM26" s="5">
         <v>0</v>
       </c>
       <c r="AN26" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO26" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AP26" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ26" s="5">
-        <v>5.1999999999999998E-3</v>
+        <v>0.0052</v>
       </c>
       <c r="AR26" s="3" t="s">
         <v>56</v>
@@ -4722,7 +4742,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:46" s="2" customFormat="1" ht="121.5">
+    <row r="27" ht="121.5" customHeight="1" s="1" customFormat="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>117</v>
@@ -4749,13 +4769,13 @@
         <v>42230</v>
       </c>
       <c r="J27" s="5">
-        <v>21.114999999999998</v>
+        <v>21.115</v>
       </c>
       <c r="K27" s="5">
-        <v>2.0199999999999999E-2</v>
+        <v>0.0202</v>
       </c>
       <c r="L27" s="5">
-        <v>47.554099999999998</v>
+        <v>47.5541</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>50</v>
@@ -4795,25 +4815,25 @@
         <v>0</v>
       </c>
       <c r="Z27" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AA27" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AB27" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AC27" s="5">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AD27" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AE27" s="5">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="AF27" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG27" s="5">
         <v>0.04</v>
@@ -4822,31 +4842,31 @@
         <v>0.01</v>
       </c>
       <c r="AI27" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ27" s="5">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="AK27" s="5">
         <v>0</v>
       </c>
       <c r="AL27" s="5">
-        <v>2.8999999999999998E-3</v>
+        <v>0.0029</v>
       </c>
       <c r="AM27" s="5">
         <v>0</v>
       </c>
       <c r="AN27" s="5">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="AO27" s="5">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP27" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ27" s="5">
-        <v>4.1999999999999997E-3</v>
+        <v>0.0042</v>
       </c>
       <c r="AR27" s="3" t="s">
         <v>128</v>
@@ -4858,7 +4878,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:46" s="2" customFormat="1" ht="87.75">
+    <row r="28" ht="87.75" customHeight="1" s="1" customFormat="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>129</v>
@@ -4888,7 +4908,7 @@
         <v>6.26</v>
       </c>
       <c r="K28" s="5">
-        <v>1.6299999999999999E-2</v>
+        <v>0.0163</v>
       </c>
       <c r="L28" s="5">
         <v>47.1875</v>
@@ -4933,58 +4953,58 @@
         <v>0</v>
       </c>
       <c r="Z28" s="5">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AA28" s="5">
         <v>0.125</v>
       </c>
       <c r="AB28" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC28" s="5">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AD28" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE28" s="5">
         <v>0.124</v>
       </c>
       <c r="AF28" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG28" s="5">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="AH28" s="5">
         <v>0.01</v>
       </c>
       <c r="AI28" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ28" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AK28" s="5">
         <v>0</v>
       </c>
       <c r="AL28" s="5">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AM28" s="5">
         <v>0</v>
       </c>
       <c r="AN28" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO28" s="5">
-        <v>1.6999999999999999E-3</v>
+        <v>0.0017</v>
       </c>
       <c r="AP28" s="5">
-        <v>5.4999999999999997E-3</v>
+        <v>0.0055</v>
       </c>
       <c r="AQ28" s="5">
-        <v>6.4999999999999997E-3</v>
+        <v>0.0065</v>
       </c>
       <c r="AR28" s="3" t="s">
         <v>128</v>
@@ -4996,7 +5016,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:46" s="2" customFormat="1" ht="231.75">
+    <row r="29" ht="231.75" customHeight="1" s="1" customFormat="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>134</v>
@@ -5026,10 +5046,10 @@
         <v>21.3</v>
       </c>
       <c r="K29" s="5">
-        <v>2.75E-2</v>
+        <v>0.0275</v>
       </c>
       <c r="L29" s="5">
-        <v>50.857999999999997</v>
+        <v>50.858</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>135</v>
@@ -5050,7 +5070,7 @@
         <v>55</v>
       </c>
       <c r="S29" s="5">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="T29" s="5">
         <v>47</v>
@@ -5071,58 +5091,58 @@
         <v>0</v>
       </c>
       <c r="Z29" s="5">
-        <v>3.3999999999999998E-3</v>
+        <v>0.0034</v>
       </c>
       <c r="AA29" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AB29" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC29" s="5">
-        <v>1.1999999999999999E-3</v>
+        <v>0.0012</v>
       </c>
       <c r="AD29" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE29" s="5">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="AF29" s="5">
         <v>0.03</v>
       </c>
       <c r="AG29" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AH29" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI29" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ29" s="5">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AK29" s="5">
         <v>0</v>
       </c>
       <c r="AL29" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AM29" s="5">
         <v>0</v>
       </c>
       <c r="AN29" s="5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="AO29" s="5">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AP29" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ29" s="5">
-        <v>5.7999999999999996E-3</v>
+        <v>0.0058</v>
       </c>
       <c r="AR29" s="3" t="s">
         <v>56</v>
@@ -5134,7 +5154,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:46" s="2" customFormat="1" ht="253.5">
+    <row r="30" ht="253.5" customHeight="1" s="1" customFormat="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>134</v>
@@ -5164,7 +5184,7 @@
         <v>21.395</v>
       </c>
       <c r="K30" s="5">
-        <v>2.7900000000000001E-2</v>
+        <v>0.0279</v>
       </c>
       <c r="L30" s="5">
         <v>50.9375</v>
@@ -5209,58 +5229,58 @@
         <v>42</v>
       </c>
       <c r="Z30" s="5">
-        <v>3.8E-3</v>
+        <v>0.0038</v>
       </c>
       <c r="AA30" s="5">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AB30" s="5">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC30" s="5">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD30" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="AE30" s="5">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="AF30" s="5">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AG30" s="5">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AH30" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI30" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ30" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK30" s="5">
         <v>0</v>
       </c>
       <c r="AL30" s="5">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AM30" s="5">
         <v>0</v>
       </c>
       <c r="AN30" s="5">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="AO30" s="5">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AP30" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ30" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AR30" s="3" t="s">
         <v>56</v>
@@ -5272,7 +5292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:46" s="2" customFormat="1" ht="243">
+    <row r="31" ht="243" customHeight="1" s="1" customFormat="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>134</v>
@@ -5302,10 +5322,10 @@
         <v>21.3</v>
       </c>
       <c r="K31" s="5">
-        <v>2.7900000000000001E-2</v>
+        <v>0.0279</v>
       </c>
       <c r="L31" s="5">
-        <v>50.857500000000002</v>
+        <v>50.8575</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>135</v>
@@ -5347,58 +5367,58 @@
         <v>43</v>
       </c>
       <c r="Z31" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AA31" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="AB31" s="5">
         <v>0.01</v>
       </c>
       <c r="AC31" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD31" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AE31" s="5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="AF31" s="5">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AG31" s="5">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AH31" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI31" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ31" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AK31" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL31" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AM31" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN31" s="5">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="AO31" s="5">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AP31" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ31" s="5">
-        <v>4.7000000000000002E-3</v>
+        <v>0.0047</v>
       </c>
       <c r="AR31" s="3" t="s">
         <v>56</v>
@@ -5410,7 +5430,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:46" s="2" customFormat="1" ht="264.75">
+    <row r="32" ht="264.75" customHeight="1" s="1" customFormat="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>134</v>
@@ -5440,7 +5460,7 @@
         <v>20.965</v>
       </c>
       <c r="K32" s="5">
-        <v>2.7799999999999998E-2</v>
+        <v>0.0278</v>
       </c>
       <c r="L32" s="5">
         <v>50.9375</v>
@@ -5485,58 +5505,58 @@
         <v>43</v>
       </c>
       <c r="Z32" s="5">
-        <v>4.1000000000000003E-3</v>
+        <v>0.0041</v>
       </c>
       <c r="AA32" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AB32" s="5">
         <v>0.01</v>
       </c>
       <c r="AC32" s="5">
-        <v>6.9999999999999999E-4</v>
+        <v>0.0007</v>
       </c>
       <c r="AD32" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AE32" s="5">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="AF32" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AG32" s="5">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AH32" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI32" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ32" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AK32" s="5">
         <v>0</v>
       </c>
       <c r="AL32" s="5">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AM32" s="5">
         <v>0</v>
       </c>
       <c r="AN32" s="5">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AO32" s="5">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP32" s="5">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ32" s="5">
-        <v>4.1000000000000003E-3</v>
+        <v>0.0041</v>
       </c>
       <c r="AR32" s="3" t="s">
         <v>56</v>
@@ -5548,237 +5568,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" ht="12"/>
+    <row r="33" ht="12" customHeight="1" s="1" customFormat="1"/>
   </sheetData>
-  <autoFilter ref="A1:AU32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AU32"/>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
+  <extLst/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99F191F-4A67-4AF3-8BDF-FD658EE75903}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1">
-        <f>COUNTA('Excess List'!C1:C32)</f>
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006A996401455D8D44A169477D654C54DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="427b0f0dcc80dd9a75fb73223d41b403">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de5e64243c8b017c27e62ae610adbab9" ns2:_="">
-    <xsd:import namespace="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:Kind" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Kind" ma:index="15" nillable="true" ma:displayName="Kind" ma:internalName="Kind">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ec2506c3-735d-4e70-aa79-204d06275b9f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Kind xmlns="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FACAD63-98F8-4CCD-93C3-2811517787F7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C40534-6BD8-4FE0-9BF5-0CFD475F6554}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED58CB96-8C6F-495B-B77F-33A6167E8BAE}"/>
 </file>